--- a/table1.xlsx
+++ b/table1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t xml:space="preserve">
 </t>
@@ -46,7 +46,10 @@
     <t xml:space="preserve">    Rural</t>
   </si>
   <si>
-    <t xml:space="preserve">n (%)</t>
+    <t xml:space="preserve">n/N (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
   </si>
   <si>
     <t xml:space="preserve">Black
@@ -61,22 +64,22 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">50,589 (33%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104,549 (67%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142,914 (92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,784 (5.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,987 (1.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,248 (0.8%)</t>
+    <t xml:space="preserve">50,589.0/155,138.0 (32.6%) (32.4%, 32.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104,549.0/155,138.0 (67.4%) (67.2%, 67.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142,914.0/154,933.0 (92.2%) (92.1%, 92.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,784.0/154,933.0 (5.0%) (4.92%, 5.13%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,987.0/154,933.0 (1.9%) (1.86%, 2.00%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,248.0/154,933.0 (0.8%) (0.762%, 0.852%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -84,22 +87,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">42,478 (35%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77,903 (65%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110,612 (92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,347 (5.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,303 (1.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">922 (0.8%)</t>
+    <t xml:space="preserve">42,478.0/120,381.0 (35.3%) (35.0%, 35.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77,903.0/120,381.0 (64.7%) (64.4%, 65.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110,612.0/120,184.0 (92.0%) (91.9%, 92.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,347.0/120,184.0 (5.3%) (5.16%, 5.41%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,303.0/120,184.0 (1.9%) (1.84%, 2.00%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922.0/120,184.0 (0.8%) (0.719%, 0.819%)</t>
   </si>
   <si>
     <t xml:space="preserve">White
@@ -111,22 +114,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">840,242 (30%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,959,218 (70%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,148,762 (77%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334,800 (12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169,606 (6.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142,537 (5.1%)</t>
+    <t xml:space="preserve">840,242.0/2,799,460.0 (30.0%) (30.0%, 30.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,959,218.0/2,799,460.0 (70.0%) (69.9%, 70.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,148,762.0/2,795,705.0 (76.9%) (76.8%, 76.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334,800.0/2,795,705.0 (12.0%) (11.9%, 12.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169,606.0/2,795,705.0 (6.1%) (6.04%, 6.09%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142,537.0/2,795,705.0 (5.1%) (5.07%, 5.12%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -134,22 +137,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">626,305 (27%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,711,631 (73%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,830,984 (78%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265,987 (11%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130,067 (5.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107,323 (4.6%)</t>
+    <t xml:space="preserve">626,305.0/2,337,936.0 (26.8%) (26.7%, 26.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,711,631.0/2,337,936.0 (73.2%) (73.2%, 73.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,830,984.0/2,334,361.0 (78.4%) (78.4%, 78.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265,987.0/2,334,361.0 (11.4%) (11.4%, 11.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130,067.0/2,334,361.0 (5.6%) (5.54%, 5.60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107,323.0/2,334,361.0 (4.6%) (4.57%, 4.62%)</t>
   </si>
   <si>
     <t xml:space="preserve">Other
@@ -161,22 +164,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">201,561 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201,234 (50%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369,636 (92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,105 (5.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,104 (1.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,404 (1.3%)</t>
+    <t xml:space="preserve">201,561.0/402,795.0 (50.0%) (49.9%, 50.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201,234.0/402,795.0 (50.0%) (49.8%, 50.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369,636.0/402,249.0 (91.9%) (91.8%, 92.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,105.0/402,249.0 (5.0%) (4.93%, 5.07%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,104.0/402,249.0 (1.8%) (1.73%, 1.81%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,404.0/402,249.0 (1.3%) (1.31%, 1.38%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -184,22 +187,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">179,785 (48%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197,159 (52%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350,851 (93%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,447 (4.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,402 (1.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,561 (0.9%)</t>
+    <t xml:space="preserve">179,785.0/376,944.0 (47.7%) (47.5%, 47.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197,159.0/376,944.0 (52.3%) (52.1%, 52.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350,851.0/376,261.0 (93.2%) (93.2%, 93.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,447.0/376,261.0 (4.4%) (4.31%, 4.44%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,402.0/376,261.0 (1.4%) (1.40%, 1.47%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,561.0/376,261.0 (0.9%) (0.916%, 0.978%)</t>
   </si>
 </sst>
 </file>
@@ -235,7 +238,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -309,6 +312,20 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="none">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="none">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="none">
         <color rgb="FF000000"/>
       </bottom>
@@ -317,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
@@ -335,6 +352,9 @@
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -655,230 +675,230 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>42</v>
+      <c r="B1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>50</v>
+      <c r="B2" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>13</v>
+      <c r="B3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>51</v>
+      <c r="B4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>52</v>
+      <c r="B5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>13</v>
+      <c r="B6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>53</v>
+      <c r="B7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>54</v>
+      <c r="B8" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>55</v>
+      <c r="B9" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>56</v>
+      <c r="B10" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G10" s="12" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
@@ -904,9 +924,33 @@
         <v>10</v>
       </c>
     </row>
+    <row r="12" ht="NA" customHeight="1">
+      <c r="A12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>

--- a/table1.xlsx
+++ b/table1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t xml:space="preserve">
 </t>
@@ -46,7 +46,7 @@
     <t xml:space="preserve">    Rural</t>
   </si>
   <si>
-    <t xml:space="preserve">n/N (%)</t>
+    <t xml:space="preserve">n (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
@@ -64,22 +64,22 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">50,589.0/155,138.0 (32.6%) (32.4%, 32.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104,549.0/155,138.0 (67.4%) (67.2%, 67.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142,914.0/154,933.0 (92.2%) (92.1%, 92.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,784.0/154,933.0 (5.0%) (4.92%, 5.13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,987.0/154,933.0 (1.9%) (1.86%, 2.00%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,248.0/154,933.0 (0.8%) (0.762%, 0.852%)</t>
+    <t xml:space="preserve">50,589 (32.6%) (32.4%, 32.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104,549 (67.4%) (67.2%, 67.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142,914 (92.2%) (92.1%, 92.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,784 (5.0%) (4.92%, 5.13%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,987 (1.9%) (1.86%, 2.00%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,248 (0.8%) (0.762%, 0.852%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -87,22 +87,45 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">42,478.0/120,381.0 (35.3%) (35.0%, 35.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77,903.0/120,381.0 (64.7%) (64.4%, 65.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110,612.0/120,184.0 (92.0%) (91.9%, 92.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,347.0/120,184.0 (5.3%) (5.16%, 5.41%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,303.0/120,184.0 (1.9%) (1.84%, 2.00%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">922.0/120,184.0 (0.8%) (0.719%, 0.819%)</t>
+    <t xml:space="preserve">42,478 (35.3%) (35.0%, 35.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77,903 (64.7%) (64.4%, 65.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110,612 (92.0%) (91.9%, 92.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,347 (5.3%) (5.16%, 5.41%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,303 (1.9%) (1.84%, 2.00%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922 (0.8%) (0.719%, 0.819%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall
+N = 275519 (100%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93,067 (33.8%) (33.6%, 34.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182,452 (66.2%) (66.0%, 66.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253,526 (92.2%) (92.1%, 92.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,131 (5.1%) (5.05%, 5.22%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,290 (1.9%) (1.87%, 1.97%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,170 (0.8%) (0.756%, 0.823%)</t>
   </si>
   <si>
     <t xml:space="preserve">White
@@ -114,22 +137,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">840,242.0/2,799,460.0 (30.0%) (30.0%, 30.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,959,218.0/2,799,460.0 (70.0%) (69.9%, 70.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,148,762.0/2,795,705.0 (76.9%) (76.8%, 76.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334,800.0/2,795,705.0 (12.0%) (11.9%, 12.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169,606.0/2,795,705.0 (6.1%) (6.04%, 6.09%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142,537.0/2,795,705.0 (5.1%) (5.07%, 5.12%)</t>
+    <t xml:space="preserve">840,242 (30.0%) (30.0%, 30.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,959,218 (70.0%) (69.9%, 70.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,148,762 (76.9%) (76.8%, 76.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334,800 (12.0%) (11.9%, 12.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169,606 (6.1%) (6.04%, 6.09%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142,537 (5.1%) (5.07%, 5.12%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -137,22 +160,45 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">626,305.0/2,337,936.0 (26.8%) (26.7%, 26.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,711,631.0/2,337,936.0 (73.2%) (73.2%, 73.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,830,984.0/2,334,361.0 (78.4%) (78.4%, 78.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265,987.0/2,334,361.0 (11.4%) (11.4%, 11.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130,067.0/2,334,361.0 (5.6%) (5.54%, 5.60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107,323.0/2,334,361.0 (4.6%) (4.57%, 4.62%)</t>
+    <t xml:space="preserve">626,305 (26.8%) (26.7%, 26.8%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,711,631 (73.2%) (73.2%, 73.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,830,984 (78.4%) (78.4%, 78.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265,987 (11.4%) (11.4%, 11.4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130,067 (5.6%) (5.54%, 5.60%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107,323 (4.6%) (4.57%, 4.62%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall
+N = 5137396 (100%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,466,547 (28.5%) (28.5%, 28.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,670,849 (71.5%) (71.4%, 71.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,979,746 (77.6%) (77.5%, 77.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600,787 (11.7%) (11.7%, 11.7%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299,673 (5.8%) (5.82%, 5.86%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249,860 (4.9%) (4.85%, 4.89%)</t>
   </si>
   <si>
     <t xml:space="preserve">Other
@@ -164,22 +210,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">201,561.0/402,795.0 (50.0%) (49.9%, 50.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201,234.0/402,795.0 (50.0%) (49.8%, 50.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369,636.0/402,249.0 (91.9%) (91.8%, 92.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,105.0/402,249.0 (5.0%) (4.93%, 5.07%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,104.0/402,249.0 (1.8%) (1.73%, 1.81%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,404.0/402,249.0 (1.3%) (1.31%, 1.38%)</t>
+    <t xml:space="preserve">201,561 (50.0%) (49.9%, 50.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201,234 (50.0%) (49.8%, 50.1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369,636 (91.9%) (91.8%, 92.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,105 (5.0%) (4.93%, 5.07%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,104 (1.8%) (1.73%, 1.81%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,404 (1.3%) (1.31%, 1.38%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -187,22 +233,45 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">179,785.0/376,944.0 (47.7%) (47.5%, 47.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197,159.0/376,944.0 (52.3%) (52.1%, 52.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350,851.0/376,261.0 (93.2%) (93.2%, 93.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,447.0/376,261.0 (4.4%) (4.31%, 4.44%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,402.0/376,261.0 (1.4%) (1.40%, 1.47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,561.0/376,261.0 (0.9%) (0.916%, 0.978%)</t>
+    <t xml:space="preserve">179,785 (47.7%) (47.5%, 47.9%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197,159 (52.3%) (52.1%, 52.5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350,851 (93.2%) (93.2%, 93.3%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,447 (4.4%) (4.31%, 4.44%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,402 (1.4%) (1.40%, 1.47%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,561 (0.9%) (0.916%, 0.978%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall
+N = 779739 (100%)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">381,346 (48.9%) (48.8%, 49.0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398,393 (51.1%) (51.0%, 51.2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720,487 (92.5%) (92.5%, 92.6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36,552 (4.7%) (4.65%, 4.74%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,506 (1.6%) (1.58%, 1.63%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,965 (1.2%) (1.13%, 1.18%)</t>
   </si>
 </sst>
 </file>
@@ -219,13 +288,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <b/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
@@ -669,6 +738,9 @@
     <col min="5" max="5" width="10.71" hidden="0" customWidth="1"/>
     <col min="6" max="6" width="10.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="10.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="10.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="NA" customHeight="1">
@@ -682,16 +754,25 @@
         <v>12</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>43</v>
+        <v>35</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -705,16 +786,25 @@
         <v>21</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>36</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -739,6 +829,15 @@
       <c r="G3" s="10" t="s">
         <v>14</v>
       </c>
+      <c r="H3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
       <c r="A4" s="4" t="s">
@@ -751,16 +850,25 @@
         <v>22</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>37</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -774,16 +882,25 @@
         <v>23</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5" s="11" t="s">
         <v>38</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -808,6 +925,15 @@
       <c r="G6" s="11" t="s">
         <v>14</v>
       </c>
+      <c r="H6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
       <c r="A7" s="4" t="s">
@@ -820,16 +946,25 @@
         <v>24</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7" s="11" t="s">
         <v>39</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -843,16 +978,25 @@
         <v>25</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>40</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
+      </c>
+      <c r="H8" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="11" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
@@ -866,16 +1010,25 @@
         <v>26</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>41</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
@@ -889,16 +1042,25 @@
         <v>27</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="12" t="s">
         <v>42</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>57</v>
+        <v>56</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
@@ -923,6 +1085,15 @@
       <c r="G11" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="H11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="12" ht="NA" customHeight="1">
       <c r="A12" s="7" t="s">
@@ -946,14 +1117,23 @@
       <c r="G12" s="7" t="s">
         <v>11</v>
       </c>
+      <c r="H12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A11:G11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="H1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/table1.xlsx
+++ b/table1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t xml:space="preserve">
 </t>
@@ -47,9 +47,6 @@
   </si>
   <si>
     <t xml:space="preserve">n (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
   </si>
   <si>
     <t xml:space="preserve">Black
@@ -64,22 +61,22 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">50,589 (32.6%) (32.4%, 32.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">104,549 (67.4%) (67.2%, 67.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142,914 (92.2%) (92.1%, 92.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,784 (5.0%) (4.92%, 5.13%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,987 (1.9%) (1.86%, 2.00%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,248 (0.8%) (0.762%, 0.852%)</t>
+    <t xml:space="preserve">50,589 (33%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104,549 (67%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142,914 (92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,784 (5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,987 (2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,248 (1%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -87,22 +84,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">42,478 (35.3%) (35.0%, 35.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77,903 (64.7%) (64.4%, 65.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">110,612 (92.0%) (91.9%, 92.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,347 (5.3%) (5.16%, 5.41%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,303 (1.9%) (1.84%, 2.00%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">922 (0.8%) (0.719%, 0.819%)</t>
+    <t xml:space="preserve">42,478 (35%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77,903 (65%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110,612 (92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,347 (5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,303 (2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">922 (1%)</t>
   </si>
   <si>
     <t xml:space="preserve">Overall
@@ -110,22 +107,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">93,067 (33.8%) (33.6%, 34.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">182,452 (66.2%) (66.0%, 66.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">253,526 (92.2%) (92.1%, 92.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14,131 (5.1%) (5.05%, 5.22%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,290 (1.9%) (1.87%, 1.97%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,170 (0.8%) (0.756%, 0.823%)</t>
+    <t xml:space="preserve">93,067 (34%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">182,452 (66%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">253,526 (92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14,131 (5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,290 (2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,170 (1%)</t>
   </si>
   <si>
     <t xml:space="preserve">White
@@ -137,22 +134,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">840,242 (30.0%) (30.0%, 30.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,959,218 (70.0%) (69.9%, 70.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,148,762 (76.9%) (76.8%, 76.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">334,800 (12.0%) (11.9%, 12.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">169,606 (6.1%) (6.04%, 6.09%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142,537 (5.1%) (5.07%, 5.12%)</t>
+    <t xml:space="preserve">840,242 (30%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,959,218 (70%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,148,762 (77%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">334,800 (12%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">169,606 (6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142,537 (5%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -160,22 +157,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">626,305 (26.8%) (26.7%, 26.8%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,711,631 (73.2%) (73.2%, 73.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,830,984 (78.4%) (78.4%, 78.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">265,987 (11.4%) (11.4%, 11.4%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">130,067 (5.6%) (5.54%, 5.60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">107,323 (4.6%) (4.57%, 4.62%)</t>
+    <t xml:space="preserve">626,305 (27%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,711,631 (73%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,830,984 (78%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265,987 (11%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130,067 (6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107,323 (5%)</t>
   </si>
   <si>
     <t xml:space="preserve">Overall
@@ -183,22 +180,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">1,466,547 (28.5%) (28.5%, 28.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,670,849 (71.5%) (71.4%, 71.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,979,746 (77.6%) (77.5%, 77.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">600,787 (11.7%) (11.7%, 11.7%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">299,673 (5.8%) (5.82%, 5.86%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">249,860 (4.9%) (4.85%, 4.89%)</t>
+    <t xml:space="preserve">1,466,547 (29%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,670,849 (71%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,979,746 (78%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600,787 (12%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299,673 (6%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">249,860 (5%)</t>
   </si>
   <si>
     <t xml:space="preserve">Other
@@ -210,22 +207,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">201,561 (50.0%) (49.9%, 50.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201,234 (50.0%) (49.8%, 50.1%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">369,636 (91.9%) (91.8%, 92.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20,105 (5.0%) (4.93%, 5.07%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,104 (1.8%) (1.73%, 1.81%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,404 (1.3%) (1.31%, 1.38%)</t>
+    <t xml:space="preserve">201,561 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">201,234 (50%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">369,636 (92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20,105 (5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,104 (2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,404 (1%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -233,22 +230,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">179,785 (47.7%) (47.5%, 47.9%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">197,159 (52.3%) (52.1%, 52.5%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">350,851 (93.2%) (93.2%, 93.3%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16,447 (4.4%) (4.31%, 4.44%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,402 (1.4%) (1.40%, 1.47%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,561 (0.9%) (0.916%, 0.978%)</t>
+    <t xml:space="preserve">179,785 (48%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">197,159 (52%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350,851 (93%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16,447 (4%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,402 (1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,561 (1%)</t>
   </si>
   <si>
     <t xml:space="preserve">Overall
@@ -256,22 +253,22 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">381,346 (48.9%) (48.8%, 49.0%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">398,393 (51.1%) (51.0%, 51.2%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">720,487 (92.5%) (92.5%, 92.6%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36,552 (4.7%) (4.65%, 4.74%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,506 (1.6%) (1.58%, 1.63%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,965 (1.2%) (1.13%, 1.18%)</t>
+    <t xml:space="preserve">381,346 (49%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">398,393 (51%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">720,487 (93%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36,552 (5%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12,506 (2%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,965 (1%)</t>
   </si>
 </sst>
 </file>
@@ -307,7 +304,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -381,20 +378,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="none">
         <color rgb="FF000000"/>
       </bottom>
@@ -403,7 +386,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
@@ -421,9 +404,6 @@
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -747,320 +727,320 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>57</v>
+      <c r="B1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>72</v>
+      <c r="B2" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>14</v>
+      <c r="B3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>73</v>
+      <c r="B4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>74</v>
+      <c r="B5" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="11" t="s">
-        <v>14</v>
+      <c r="B6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J7" s="11" t="s">
-        <v>75</v>
+      <c r="B7" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="11" t="s">
-        <v>76</v>
+      <c r="B8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" s="11" t="s">
-        <v>77</v>
+      <c r="B9" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
       <c r="A10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>78</v>
+      <c r="B10" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
@@ -1095,42 +1075,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" ht="NA" customHeight="1">
-      <c r="A12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A11:J11"/>
-    <mergeCell ref="A12:J12"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>

--- a/table1.xlsx
+++ b/table1.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="88">
   <si>
     <t xml:space="preserve">
 </t>
@@ -46,11 +46,27 @@
     <t xml:space="preserve">    Rural</t>
   </si>
   <si>
+    <t xml:space="preserve">    Unknown</t>
+  </si>
+  <si>
     <t xml:space="preserve">n (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Black
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Missing
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (0%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">402 (0.1%)</t>
   </si>
   <si>
     <t xml:space="preserve">F
@@ -58,9 +74,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">50,589 (33%)</t>
   </si>
   <si>
@@ -129,6 +142,9 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">7,330 (0.1%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">F
 N = 2799460 (54%)
 </t>
@@ -152,6 +168,9 @@
     <t xml:space="preserve">142,537 (5%)</t>
   </si>
   <si>
+    <t xml:space="preserve">3,755</t>
+  </si>
+  <si>
     <t xml:space="preserve">M
 N = 2337936 (46%)
 </t>
@@ -175,6 +194,9 @@
     <t xml:space="preserve">107,323 (5%)</t>
   </si>
   <si>
+    <t xml:space="preserve">3,575</t>
+  </si>
+  <si>
     <t xml:space="preserve">Overall
 N = 5137396 (100%)
 </t>
@@ -198,8 +220,14 @@
     <t xml:space="preserve">249,860 (5%)</t>
   </si>
   <si>
+    <t xml:space="preserve">7,330</t>
+  </si>
+  <si>
     <t xml:space="preserve">Other
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,229 (0.2%)</t>
   </si>
   <si>
     <t xml:space="preserve">F
@@ -269,6 +297,9 @@
   </si>
   <si>
     <t xml:space="preserve">8,965 (1%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,229</t>
   </si>
 </sst>
 </file>
@@ -721,6 +752,9 @@
     <col min="8" max="8" width="10.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="10.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="10.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="10.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="10.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="10.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="NA" customHeight="1">
@@ -728,31 +762,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="F1" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>56</v>
+        <v>64</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
@@ -760,31 +803,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>71</v>
+        <v>13</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="L2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="8" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
@@ -792,31 +844,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
@@ -824,31 +885,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>72</v>
+        <v>15</v>
+      </c>
+      <c r="K4" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="L4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
@@ -859,28 +929,37 @@
         <v>15</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="J5" s="10" t="s">
-        <v>73</v>
+        <v>15</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
@@ -888,31 +967,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I6" s="10" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J6" s="10" t="s">
-        <v>13</v>
+        <v>65</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
@@ -920,31 +1008,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J7" s="10" t="s">
-        <v>74</v>
+        <v>15</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="L7" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -952,31 +1049,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="J8" s="10" t="s">
-        <v>75</v>
+        <v>15</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="L8" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="9" ht="NA" customHeight="1">
@@ -984,103 +1090,171 @@
         <v>8</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>76</v>
+        <v>15</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="10" ht="NA" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="J10" s="11" t="s">
-        <v>77</v>
+      <c r="B10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="11" ht="NA" customHeight="1">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>10</v>
+      <c r="B11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>205</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>197</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>402</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="K11" s="11" t="n">
+        <v>546</v>
+      </c>
+      <c r="L11" s="11" t="n">
+        <v>683</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" ht="NA" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A11:J11"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="H1:J1"/>
+    <mergeCell ref="A12:M12"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
